--- a/StructureDefinition-openelis-task.xlsx
+++ b/StructureDefinition-openelis-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-task.xlsx
+++ b/StructureDefinition-openelis-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -487,7 +487,7 @@
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -561,7 +561,7 @@
     <t>Task.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Task)
+    <t xml:space="preserve">Reference(Task|4.0.1)
 </t>
   </si>
   <si>
@@ -735,7 +735,7 @@
     <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
+    <t>http://hl7.org/fhir/ValueSet/task-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -766,7 +766,7 @@
     <t>Task.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -820,7 +820,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -922,7 +922,7 @@
     <t>Task.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.role, Request.performerType</t>
@@ -1003,7 +1003,7 @@
     <t>Task.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1070,7 +1070,7 @@
     <t>Task.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -1115,7 +1115,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1234,7 +1234,7 @@
     <t>Task.restriction.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Group|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>

--- a/StructureDefinition-openelis-task.xlsx
+++ b/StructureDefinition-openelis-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-task.xlsx
+++ b/StructureDefinition-openelis-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-task.xlsx
+++ b/StructureDefinition-openelis-task.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
